--- a/estore_schemes/2/params.xlsx
+++ b/estore_schemes/2/params.xlsx
@@ -63657,7 +63657,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -63672,7 +63672,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>300</v>
+        <v>3600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -63687,7 +63687,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -63702,7 +63702,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -63734,7 +63734,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -63893,7 +63893,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -63908,7 +63908,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -63923,7 +63923,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -63938,7 +63938,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/estore_schemes/2/params.xlsx
+++ b/estore_schemes/2/params.xlsx
@@ -6951,228 +6951,228 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>参数</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>值</t>
         </is>
       </c>
-      <c r="C1" s="0" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>solver</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>求解器</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="B3" s="0" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>dayahead_24h</t>
         </is>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>模式</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>experiment</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>perspective_i2r_block20</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>实验配置</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>dt_minutes</t>
         </is>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" t="n">
         <v>15</v>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>时间步长(分钟)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>time_limit</t>
         </is>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" t="n">
         <v>3600</v>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>时间上限(秒)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>mip_gap</t>
         </is>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>MIP Gap</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>current_segments</t>
         </is>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>电流分段数</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>current_mode</t>
         </is>
       </c>
-      <c r="B9" s="0" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>电流模式</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>soc_grid_width</t>
         </is>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" t="n">
         <v>0.3</v>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>SOC网格宽度</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>threads</t>
         </is>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>线程数</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>mip_focus</t>
         </is>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="0" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>MIP Focus</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>cuts</t>
         </is>
       </c>
-      <c r="C13" s="0" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Cuts</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>heuristics</t>
         </is>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" t="n">
         <v>0.3</v>
       </c>
-      <c r="C14" s="0" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Heuristics</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>hours</t>
         </is>
@@ -7180,67 +7180,127 @@
       <c r="B15" t="n">
         <v>72</v>
       </c>
-      <c r="C15" s="0" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>时域覆盖(小时)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>initial_soc</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>电池初始SOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>initial_t_bat_c</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>电芯初始温度(℃)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>initial_t_tank_c</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>液冷罐初始温度(℃)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>initial_t_cont_c</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>舱体初始温度(℃)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>strict_current_sos2</t>
         </is>
       </c>
-      <c r="B16" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C16" s="0" t="inlineStr">
+      <c r="B20" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>严格电流SOS2</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="0" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>tight_temp_bounds</t>
         </is>
       </c>
-      <c r="B17" s="0" t="b">
+      <c r="B21" t="b">
         <v>1</v>
       </c>
-      <c r="C17" s="0" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>使用紧温度边界</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>build_only</t>
         </is>
       </c>
-      <c r="B18" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
+      <c r="B22" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>仅建模检查</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="0" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>no_plots</t>
         </is>
       </c>
-      <c r="B19" s="0" t="b">
+      <c r="B23" t="b">
         <v>1</v>
       </c>
-      <c r="C19" s="0" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>跳过图形输出</t>
         </is>
@@ -7408,13 +7468,13 @@
         <v>4</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>1689.984</v>
+        <v>689.984</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>0.583</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.01586</v>
+        <v>0.02586</v>
       </c>
       <c r="H2" s="6" t="n">
         <v>0.008</v>

--- a/estore_schemes/2/params.xlsx
+++ b/estore_schemes/2/params.xlsx
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/estore_schemes/2/params.xlsx
+++ b/estore_schemes/2/params.xlsx
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
